--- a/artfynd/A 20023-2026 artfynd.xlsx
+++ b/artfynd/A 20023-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>81811677</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517416.5399973054</v>
+        <v>517417</v>
       </c>
       <c r="R2" t="n">
-        <v>6900478.849364066</v>
+        <v>6900479</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-09-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81811717</v>
+        <v>81811679</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517690.4457790019</v>
+        <v>517527</v>
       </c>
       <c r="R3" t="n">
-        <v>6900508.25007509</v>
+        <v>6900499</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81811678</v>
+        <v>81811717</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517521.941019887</v>
+        <v>517690</v>
       </c>
       <c r="R4" t="n">
-        <v>6900500.841701766</v>
+        <v>6900508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81811679</v>
+        <v>82278004</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517527.0862722055</v>
+        <v>517691</v>
       </c>
       <c r="R5" t="n">
-        <v>6900499.003703391</v>
+        <v>6900508</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,15 +1051,112 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Granér, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>81811678</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grubban, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>517522</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6900501</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Malin Löfgren</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Malin Löfgren</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20023-2026 artfynd.xlsx
+++ b/artfynd/A 20023-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81811677</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81811679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81811717</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82278004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81811678</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>